--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1103,45 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573136</v>
+        <v>133573143</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635887</v>
+        <v>635478</v>
       </c>
       <c r="R6" t="n">
-        <v>6999395</v>
+        <v>6999310</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1173,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,8 +1195,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,48 +1229,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573143</v>
+        <v>133573136</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635478</v>
+        <v>635887</v>
       </c>
       <c r="R7" t="n">
-        <v>6999310</v>
+        <v>6999395</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1283,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,24 +1318,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R18" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R19" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566413</v>
+        <v>133566414</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>56522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,26 +2689,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2716,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635479</v>
+        <v>635429</v>
       </c>
       <c r="R20" t="n">
-        <v>6999292</v>
+        <v>6999308</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2751,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,24 +2775,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2804,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133566414</v>
+        <v>133566401</v>
       </c>
       <c r="B21" t="n">
-        <v>56522</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,42 +2804,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635730</v>
       </c>
       <c r="R21" t="n">
-        <v>6999308</v>
+        <v>6999349</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2882,7 +2863,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2873,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,7 +2900,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133573141</v>
       </c>
       <c r="B22" t="n">
         <v>79333</v>
@@ -2948,19 +2929,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635507</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999312</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2989,7 +2973,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2999,7 +2983,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,66 +2992,85 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573147</v>
+        <v>133566413</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635417</v>
+        <v>635479</v>
       </c>
       <c r="R23" t="n">
-        <v>6999294</v>
+        <v>6999292</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3096,7 +3099,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3109,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,78 +3118,82 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573133</v>
+        <v>133573147</v>
       </c>
       <c r="B24" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635907</v>
+        <v>635417</v>
       </c>
       <c r="R24" t="n">
-        <v>6999335</v>
+        <v>6999294</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3215,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,7 +3241,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3253,7 +3259,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573146</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
         <v>99130</v>
@@ -3283,7 +3289,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3300,13 +3306,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999309</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3335,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,37 +3379,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3411,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999309</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,21 +3483,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,45 +3510,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R27" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3594,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,37 +3617,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R28" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79333</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,63 +3813,87 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,51 +3962,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,34 +4051,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133566409</v>
+        <v>133573137</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635505</v>
+        <v>635611</v>
       </c>
       <c r="R3" t="n">
-        <v>6999294</v>
+        <v>6999361</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133573137</v>
+        <v>133566409</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635611</v>
+        <v>635505</v>
       </c>
       <c r="R4" t="n">
-        <v>6999361</v>
+        <v>6999294</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2678,42 +2678,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566414</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2721,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999308</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,66 +2779,79 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133566401</v>
+        <v>133573146</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635730</v>
+        <v>635429</v>
       </c>
       <c r="R21" t="n">
-        <v>6999349</v>
+        <v>6999309</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2863,7 +2880,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2890,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,28 +2899,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133573141</v>
+        <v>133566413</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,21 +2929,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,13 +2956,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635507</v>
+        <v>635479</v>
       </c>
       <c r="R22" t="n">
-        <v>6999312</v>
+        <v>6999292</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2983,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2998,79 +3016,76 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133566413</v>
+        <v>133573147</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635479</v>
+        <v>635417</v>
       </c>
       <c r="R23" t="n">
-        <v>6999292</v>
+        <v>6999294</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3099,7 +3114,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3109,7 +3124,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,66 +3133,50 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573147</v>
+        <v>133566401</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3187,13 +3186,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635417</v>
+        <v>635730</v>
       </c>
       <c r="R24" t="n">
-        <v>6999294</v>
+        <v>6999349</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3222,7 +3221,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3231,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,58 +3246,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133573141</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3306,13 +3296,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635507</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999312</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,6 +3353,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3379,46 +3384,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573146</v>
+        <v>133566414</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>56522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3429,10 +3430,10 @@
         <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999309</v>
+        <v>6999308</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,7 +3462,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3472,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,19 +3481,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3847,53 +3847,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>56522</v>
+        <v>91881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3925,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,45 +3954,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1596,7 +1604,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R18" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B19" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R19" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,46 +2678,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133566413</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635479</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,72 +2774,75 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573146</v>
+        <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>91881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R21" t="n">
-        <v>6999309</v>
+        <v>6999294</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2880,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2890,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2893,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566413</v>
+        <v>133566401</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,37 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635479</v>
+        <v>635730</v>
       </c>
       <c r="R22" t="n">
-        <v>6999292</v>
+        <v>6999349</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,24 +3000,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3044,45 +3018,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573147</v>
+        <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635417</v>
+        <v>635507</v>
       </c>
       <c r="R23" t="n">
-        <v>6999294</v>
+        <v>6999312</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3114,7 +3091,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3124,7 +3101,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3133,8 +3110,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3151,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566401</v>
+        <v>133566414</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,34 +3155,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635730</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999349</v>
+        <v>6999308</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3221,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3231,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3258,37 +3259,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573141</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3296,13 +3306,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635507</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999312</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,21 +3363,6 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3384,42 +3379,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566414</v>
+        <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>99130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3430,10 +3429,10 @@
         <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999308</v>
+        <v>6999309</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3462,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,18 +3480,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573137</v>
+        <v>133566409</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635611</v>
+        <v>635505</v>
       </c>
       <c r="R3" t="n">
-        <v>6999361</v>
+        <v>6999294</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133566409</v>
+        <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635505</v>
+        <v>635611</v>
       </c>
       <c r="R4" t="n">
-        <v>6999294</v>
+        <v>6999361</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1103,48 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573143</v>
+        <v>133573136</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635478</v>
+        <v>635887</v>
       </c>
       <c r="R6" t="n">
-        <v>6999310</v>
+        <v>6999395</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1176,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,24 +1192,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,45 +1210,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573136</v>
+        <v>133573143</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635887</v>
+        <v>635478</v>
       </c>
       <c r="R7" t="n">
-        <v>6999395</v>
+        <v>6999310</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1299,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,8 +1302,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>97995</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R18" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>97995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R19" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,37 +2678,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566413</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2716,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635479</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999292</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2774,75 +2783,72 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573147</v>
+        <v>133573146</v>
       </c>
       <c r="B21" t="n">
-        <v>91881</v>
+        <v>99130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R21" t="n">
-        <v>6999294</v>
+        <v>6999309</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2874,7 +2880,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,6 +2899,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2911,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133566414</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,34 +2929,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635429</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999308</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2981,7 +2996,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +3006,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,48 +3033,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573141</v>
+        <v>133573147</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635507</v>
+        <v>635417</v>
       </c>
       <c r="R23" t="n">
-        <v>6999312</v>
+        <v>6999294</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3091,7 +3103,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3101,7 +3113,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,24 +3122,8 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3144,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566414</v>
+        <v>133566413</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,31 +3151,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3187,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R24" t="n">
-        <v>6999308</v>
+        <v>6999292</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3222,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,8 +3232,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3259,60 +3266,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133566401</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635730</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999349</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,65 +3355,55 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573146</v>
+        <v>133573141</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3426,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R26" t="n">
-        <v>6999309</v>
+        <v>6999312</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3461,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,6 +3468,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,82 +3818,69 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133573145</v>
       </c>
       <c r="B30" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635465</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999358</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3927,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,71 +3928,79 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>91881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566416</v>
+        <v>133566392</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1604,7 +1596,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1614,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635420</v>
+        <v>635950</v>
       </c>
       <c r="R10" t="n">
-        <v>6999295</v>
+        <v>6999346</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3721,53 +3721,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>91881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,45 +3954,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1596,7 +1604,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566416</v>
+        <v>133566392</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1604,7 +1596,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1614,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635420</v>
+        <v>635950</v>
       </c>
       <c r="R10" t="n">
-        <v>6999295</v>
+        <v>6999346</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B27" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,37 +3510,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R27" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,22 +3602,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>93206</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,45 +3625,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R28" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,57 +3709,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3791,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3954,53 +3962,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>91881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573144</v>
       </c>
       <c r="B2" t="n">
-        <v>80466</v>
+        <v>80467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133566409</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133566404</v>
       </c>
       <c r="B5" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133573136</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>133573143</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,53 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1911,7 +1911,7 @@
         <v>133573139</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>133573132</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,60 +2678,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133573147</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>91883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635417</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999294</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2779,7 +2767,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2798,46 +2785,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573146</v>
+        <v>133566413</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2845,13 +2823,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R21" t="n">
-        <v>6999309</v>
+        <v>6999292</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2880,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2890,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,25 +2881,40 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566414</v>
+        <v>133566401</v>
       </c>
       <c r="B22" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,42 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635429</v>
+        <v>635730</v>
       </c>
       <c r="R22" t="n">
-        <v>6999308</v>
+        <v>6999349</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3006,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,45 +3018,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573147</v>
+        <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635417</v>
+        <v>635507</v>
       </c>
       <c r="R23" t="n">
-        <v>6999294</v>
+        <v>6999312</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3103,7 +3091,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3113,7 +3101,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,8 +3110,24 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3140,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566413</v>
+        <v>133566414</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>56522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3151,26 +3155,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3178,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635479</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999292</v>
+        <v>6999308</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3213,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3223,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,24 +3241,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3266,48 +3259,60 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133566401</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635730</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999349</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,55 +3360,65 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3411,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999309</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,21 +3483,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>57145</v>
+        <v>93208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,45 +3510,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R27" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3594,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>93206</v>
+        <v>57145</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,37 +3617,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R28" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,69 +3813,82 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,79 +3936,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4072,7 +4072,7 @@
         <v>133573140</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1571,45 +1571,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>57145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,34 +3818,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3954,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,31 +3954,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3997,13 +3981,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,18 +4035,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1571,53 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R10" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133566404</v>
       </c>
       <c r="B5" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,45 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573136</v>
+        <v>133573143</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635887</v>
+        <v>635478</v>
       </c>
       <c r="R6" t="n">
-        <v>6999395</v>
+        <v>6999310</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1173,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,8 +1195,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,48 +1229,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573143</v>
+        <v>133573136</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635478</v>
+        <v>635887</v>
       </c>
       <c r="R7" t="n">
-        <v>6999310</v>
+        <v>6999395</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1283,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,24 +1318,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1571,45 +1571,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>57145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,7 +1911,7 @@
         <v>133573139</v>
       </c>
       <c r="B13" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>133573132</v>
       </c>
       <c r="B17" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,48 +2678,56 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573147</v>
+        <v>133566414</v>
       </c>
       <c r="B20" t="n">
-        <v>91883</v>
+        <v>56522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R20" t="n">
-        <v>6999294</v>
+        <v>6999308</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2748,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,63 +2781,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133566413</v>
+        <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635479</v>
+        <v>635417</v>
       </c>
       <c r="R21" t="n">
-        <v>6999292</v>
+        <v>6999294</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,7 +2863,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2873,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2877,34 +2882,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3144,10 +3133,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566414</v>
+        <v>133566413</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,31 +3144,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3187,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R24" t="n">
-        <v>6999308</v>
+        <v>6999292</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3222,7 +3206,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3216,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,8 +3225,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3262,7 +3262,7 @@
         <v>133573133</v>
       </c>
       <c r="B25" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3836,48 +3836,51 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133573145</v>
       </c>
       <c r="B30" t="n">
-        <v>91883</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635465</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999358</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3906,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,69 +3928,82 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,34 +4051,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566416</v>
+        <v>133566392</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1604,7 +1596,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1614,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635420</v>
+        <v>635950</v>
       </c>
       <c r="R10" t="n">
-        <v>6999295</v>
+        <v>6999346</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2678,42 +2678,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566414</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2721,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999308</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2756,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,63 +2779,76 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573147</v>
+        <v>133573146</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R21" t="n">
-        <v>6999294</v>
+        <v>6999309</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2863,7 +2880,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2890,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,6 +2899,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133566413</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2929,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635479</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999292</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2970,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,8 +3010,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3007,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,26 +3055,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3045,13 +3087,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R23" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3080,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3090,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,85 +3141,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566413</v>
+        <v>133573147</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635479</v>
+        <v>635417</v>
       </c>
       <c r="R24" t="n">
-        <v>6999292</v>
+        <v>6999294</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3206,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3216,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,94 +3248,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133566401</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635730</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999349</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,65 +3355,55 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573146</v>
+        <v>133573141</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3426,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R26" t="n">
-        <v>6999309</v>
+        <v>6999312</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3461,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,6 +3468,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,69 +3813,82 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,79 +3936,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B9" t="n">
-        <v>91928</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1596,7 +1604,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2678,46 +2678,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133566413</v>
       </c>
       <c r="B20" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635479</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,72 +2774,75 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573146</v>
+        <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>99140</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R21" t="n">
-        <v>6999309</v>
+        <v>6999294</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2880,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2890,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2893,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566413</v>
+        <v>133566401</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,37 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635479</v>
+        <v>635730</v>
       </c>
       <c r="R22" t="n">
-        <v>6999292</v>
+        <v>6999349</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,24 +3000,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3044,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133566414</v>
+        <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,31 +3029,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3087,13 +3056,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R23" t="n">
-        <v>6999308</v>
+        <v>6999312</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,7 +3091,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3101,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,66 +3110,94 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573147</v>
+        <v>133573133</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>99140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635417</v>
+        <v>635907</v>
       </c>
       <c r="R24" t="n">
-        <v>6999294</v>
+        <v>6999335</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3248,6 +3245,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3266,48 +3264,60 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133566401</v>
+        <v>133573146</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635730</v>
+        <v>635429</v>
       </c>
       <c r="R25" t="n">
-        <v>6999349</v>
+        <v>6999309</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,28 +3365,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,26 +3395,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3411,13 +3427,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,7 +3462,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3472,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,34 +3481,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,82 +3818,69 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133573145</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635465</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999358</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3927,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,71 +3928,79 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3144,46 +3144,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573133</v>
+        <v>133566414</v>
       </c>
       <c r="B24" t="n">
-        <v>99140</v>
+        <v>56522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3191,13 +3187,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635907</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999335</v>
+        <v>6999308</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,26 +3241,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573146</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
         <v>99140</v>
@@ -3294,7 +3289,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3311,13 +3306,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999309</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3346,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3384,42 +3379,46 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566414</v>
+        <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3430,10 +3429,10 @@
         <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999308</v>
+        <v>6999309</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3462,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,18 +3480,19 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,69 +3813,82 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,79 +3936,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -2678,37 +2678,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566413</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2716,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635479</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999292</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2774,75 +2783,72 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573147</v>
+        <v>133573146</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R21" t="n">
-        <v>6999294</v>
+        <v>6999309</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2874,7 +2880,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2893,6 +2899,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2911,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133566413</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,34 +2929,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635479</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999292</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2981,7 +2991,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +3001,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,8 +3010,24 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3018,10 +3044,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,26 +3055,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3056,13 +3087,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R23" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3091,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3101,7 +3132,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3110,90 +3141,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566414</v>
+        <v>133573147</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R24" t="n">
-        <v>6999308</v>
+        <v>6999294</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3222,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,72 +3254,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133566401</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635730</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999349</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,65 +3355,55 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573146</v>
+        <v>133573141</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3426,10 +3411,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R26" t="n">
-        <v>6999309</v>
+        <v>6999312</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3461,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3483,6 +3468,21 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>56522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,82 +3818,69 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133573145</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635465</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999358</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3917,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3927,7 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3936,71 +3928,79 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>91928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566416</v>
+        <v>133566392</v>
       </c>
       <c r="B10" t="n">
         <v>57145</v>
@@ -1604,7 +1596,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1614,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635420</v>
+        <v>635950</v>
       </c>
       <c r="R10" t="n">
-        <v>6999295</v>
+        <v>6999346</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1649,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,45 +1678,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>57145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2678,46 +2678,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133566413</v>
       </c>
       <c r="B20" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635479</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,72 +2774,75 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573146</v>
+        <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>99140</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R21" t="n">
-        <v>6999309</v>
+        <v>6999294</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2880,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2890,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,7 +2893,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2918,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566413</v>
+        <v>133566401</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,37 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635479</v>
+        <v>635730</v>
       </c>
       <c r="R22" t="n">
-        <v>6999292</v>
+        <v>6999349</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2991,7 +2981,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3001,7 +2991,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,24 +3000,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3044,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133566414</v>
+        <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,31 +3029,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3087,13 +3056,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R23" t="n">
-        <v>6999308</v>
+        <v>6999312</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,7 +3091,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,7 +3101,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,66 +3110,90 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573147</v>
+        <v>133566414</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>56522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999294</v>
+        <v>6999308</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,7 +3222,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3232,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,60 +3247,72 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133566401</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635730</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999349</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3351,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,55 +3360,65 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133573146</v>
       </c>
       <c r="B26" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3411,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999309</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3446,7 +3461,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3471,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,21 +3483,6 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,69 +3813,82 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3927,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,79 +3936,71 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573144</v>
       </c>
       <c r="B2" t="n">
-        <v>80467</v>
+        <v>80481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133566409</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133566404</v>
       </c>
       <c r="B5" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133573143</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>133573136</v>
       </c>
       <c r="B7" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>133566394</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>133566392</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>133566418</v>
       </c>
       <c r="B12" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>133573139</v>
       </c>
       <c r="B13" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>91947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>133573149</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>133573132</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,37 +2678,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566413</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2716,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635479</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999292</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2774,30 +2783,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2807,7 +2801,7 @@
         <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2911,48 +2905,60 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133573146</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635429</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999309</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2981,7 +2987,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2991,7 +2997,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,18 +3006,19 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3021,7 +3028,7 @@
         <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,10 +3151,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566414</v>
+        <v>133566413</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,31 +3162,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3187,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R24" t="n">
-        <v>6999308</v>
+        <v>6999292</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3222,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3232,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,8 +3243,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3259,46 +3277,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133566414</v>
       </c>
       <c r="B25" t="n">
-        <v>99140</v>
+        <v>56529</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3306,13 +3320,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635429</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999308</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3341,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3360,79 +3374,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573146</v>
+        <v>133566401</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635429</v>
+        <v>635730</v>
       </c>
       <c r="R26" t="n">
-        <v>6999309</v>
+        <v>6999349</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3461,7 +3462,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3471,7 +3472,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,29 +3481,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B27" t="n">
-        <v>93216</v>
+        <v>57152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,37 +3510,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R27" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,22 +3602,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B28" t="n">
-        <v>57145</v>
+        <v>93244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,45 +3625,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R28" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>56529</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,34 +3818,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3850,7 +3839,7 @@
         <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3954,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,31 +3954,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3997,13 +3981,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R31" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,18 +4035,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
         <v>133573140</v>
       </c>
       <c r="B32" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1103,48 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573143</v>
+        <v>133573136</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635478</v>
+        <v>635887</v>
       </c>
       <c r="R6" t="n">
-        <v>6999310</v>
+        <v>6999395</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1176,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1186,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,24 +1192,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1229,45 +1210,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573136</v>
+        <v>133573143</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635887</v>
+        <v>635478</v>
       </c>
       <c r="R7" t="n">
-        <v>6999395</v>
+        <v>6999310</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1299,7 +1283,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1293,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,8 +1302,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>98033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R18" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B19" t="n">
-        <v>98033</v>
+        <v>91947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R19" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,7 +2678,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133573146</v>
       </c>
       <c r="B20" t="n">
         <v>99168</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635429</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999309</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,46 +2905,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133573146</v>
+        <v>133566413</v>
       </c>
       <c r="B22" t="n">
-        <v>99168</v>
+        <v>91947</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2952,13 +2943,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R22" t="n">
-        <v>6999309</v>
+        <v>6999292</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2987,7 +2978,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2997,7 +2988,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,25 +3001,40 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>56529</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,26 +3042,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3063,13 +3074,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R23" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,7 +3109,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,7 +3119,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,44 +3128,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566413</v>
+        <v>133566401</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,37 +3157,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635479</v>
+        <v>635730</v>
       </c>
       <c r="R24" t="n">
-        <v>6999292</v>
+        <v>6999349</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3224,7 +3216,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3226,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,24 +3235,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3277,42 +3253,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133566414</v>
+        <v>133573133</v>
       </c>
       <c r="B25" t="n">
-        <v>56529</v>
+        <v>99168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3320,13 +3300,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R25" t="n">
-        <v>6999308</v>
+        <v>6999335</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3355,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3365,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,25 +3354,26 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566401</v>
+        <v>133573141</v>
       </c>
       <c r="B26" t="n">
         <v>79348</v>
@@ -3421,19 +3402,22 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635730</v>
+        <v>635507</v>
       </c>
       <c r="R26" t="n">
-        <v>6999349</v>
+        <v>6999312</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3462,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,28 +3465,44 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>57152</v>
+        <v>93244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,45 +3510,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R27" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3594,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>93244</v>
+        <v>57152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,37 +3617,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R28" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56529</v>
+        <v>79348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,63 +3813,87 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B30" t="n">
-        <v>91910</v>
+        <v>56529</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,51 +3962,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>91910</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,34 +4051,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573144</v>
       </c>
       <c r="B2" t="n">
-        <v>80481</v>
+        <v>80477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133566409</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133566404</v>
       </c>
       <c r="B5" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,45 +1103,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133573136</v>
+        <v>133573143</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>635887</v>
+        <v>635478</v>
       </c>
       <c r="R6" t="n">
-        <v>6999395</v>
+        <v>6999310</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1173,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,8 +1195,24 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1210,48 +1229,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133573143</v>
+        <v>133573136</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>635478</v>
+        <v>635887</v>
       </c>
       <c r="R7" t="n">
-        <v>6999310</v>
+        <v>6999395</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1283,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1293,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,24 +1318,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1339,7 +1339,7 @@
         <v>133566394</v>
       </c>
       <c r="B8" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>133566392</v>
       </c>
       <c r="B10" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>133566416</v>
       </c>
       <c r="B11" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>133566418</v>
       </c>
       <c r="B12" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>133573139</v>
       </c>
       <c r="B13" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2245,7 +2245,7 @@
         <v>133573149</v>
       </c>
       <c r="B16" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>133573132</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>98033</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R18" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>91947</v>
+        <v>98043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R19" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573146</v>
+        <v>133573133</v>
       </c>
       <c r="B20" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635429</v>
+        <v>635907</v>
       </c>
       <c r="R20" t="n">
-        <v>6999309</v>
+        <v>6999335</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2801,7 +2801,7 @@
         <v>133573147</v>
       </c>
       <c r="B21" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2905,37 +2905,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566413</v>
+        <v>133573146</v>
       </c>
       <c r="B22" t="n">
-        <v>91947</v>
+        <v>99178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2943,13 +2952,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635479</v>
+        <v>635429</v>
       </c>
       <c r="R22" t="n">
-        <v>6999292</v>
+        <v>6999309</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,7 +2987,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2988,7 +2997,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,40 +3010,25 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133566414</v>
+        <v>133573141</v>
       </c>
       <c r="B23" t="n">
-        <v>56529</v>
+        <v>79358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3042,31 +3036,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3074,13 +3063,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R23" t="n">
-        <v>6999308</v>
+        <v>6999312</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3109,7 +3098,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3119,7 +3108,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,28 +3117,44 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566401</v>
+        <v>133566413</v>
       </c>
       <c r="B24" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3157,34 +3162,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635730</v>
+        <v>635479</v>
       </c>
       <c r="R24" t="n">
-        <v>6999349</v>
+        <v>6999292</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3216,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3226,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,8 +3243,24 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3253,46 +3277,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573133</v>
+        <v>133566414</v>
       </c>
       <c r="B25" t="n">
-        <v>99168</v>
+        <v>56539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3300,13 +3320,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635907</v>
+        <v>635429</v>
       </c>
       <c r="R25" t="n">
-        <v>6999335</v>
+        <v>6999308</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3335,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3354,29 +3374,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133566401</v>
       </c>
       <c r="B26" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3402,22 +3421,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635730</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999349</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,7 +3462,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3472,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,34 +3481,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3502,7 +3502,7 @@
         <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3721,10 +3721,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133573145</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>79348</v>
+        <v>56539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,26 +3732,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3759,13 +3764,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635465</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999358</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3794,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3804,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3813,87 +3818,63 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>56529</v>
+        <v>91920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3925,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3935,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3962,48 +3943,51 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133566406</v>
+        <v>133573145</v>
       </c>
       <c r="B31" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635550</v>
+        <v>635465</v>
       </c>
       <c r="R31" t="n">
-        <v>6999336</v>
+        <v>6999358</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4042,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,18 +4035,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
         <v>133573140</v>
       </c>
       <c r="B32" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566416</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635420</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999295</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,53 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566419</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635425</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999291</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566392</v>
       </c>
       <c r="B11" t="n">
         <v>57162</v>
@@ -1711,7 +1711,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635950</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999346</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>98043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R18" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B19" t="n">
-        <v>98043</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R19" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,45 +2798,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573147</v>
+        <v>133573141</v>
       </c>
       <c r="B21" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635417</v>
+        <v>635507</v>
       </c>
       <c r="R21" t="n">
-        <v>6999294</v>
+        <v>6999312</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2868,7 +2871,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2878,7 +2881,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2887,8 +2890,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2905,57 +2924,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133573146</v>
+        <v>133573147</v>
       </c>
       <c r="B22" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R22" t="n">
-        <v>6999309</v>
+        <v>6999294</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2987,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2997,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3006,7 +3013,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3025,7 +3031,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573141</v>
+        <v>133566401</v>
       </c>
       <c r="B23" t="n">
         <v>79358</v>
@@ -3054,22 +3060,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635507</v>
+        <v>635730</v>
       </c>
       <c r="R23" t="n">
-        <v>6999312</v>
+        <v>6999349</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3098,7 +3101,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3108,7 +3111,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3117,71 +3120,64 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133566413</v>
+        <v>133573146</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3189,13 +3185,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635479</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999292</v>
+        <v>6999309</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3224,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3230,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,30 +3243,15 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3392,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566401</v>
+        <v>133566413</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,34 +3384,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635730</v>
+        <v>635479</v>
       </c>
       <c r="R26" t="n">
-        <v>6999349</v>
+        <v>6999292</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3462,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3481,8 +3465,24 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B27" t="n">
-        <v>93254</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,37 +3510,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R27" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,22 +3602,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>93254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,45 +3625,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R28" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,65 +3709,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B29" t="n">
-        <v>56539</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3836,45 +3828,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>56539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133566409</v>
+        <v>133573137</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635505</v>
+        <v>635611</v>
       </c>
       <c r="R3" t="n">
-        <v>6999294</v>
+        <v>6999361</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133573137</v>
+        <v>133566409</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635611</v>
+        <v>635505</v>
       </c>
       <c r="R4" t="n">
-        <v>6999361</v>
+        <v>6999294</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1456,53 +1456,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R9" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,7 +1526,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1536,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,45 +1563,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B10" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R10" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566392</v>
+        <v>133566416</v>
       </c>
       <c r="B11" t="n">
         <v>57162</v>
@@ -1711,7 +1711,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635950</v>
+        <v>635420</v>
       </c>
       <c r="R11" t="n">
-        <v>6999346</v>
+        <v>6999295</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2464,32 +2464,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133573138</v>
+        <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>98043</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>635628</v>
+        <v>635475</v>
       </c>
       <c r="R18" t="n">
-        <v>6999359</v>
+        <v>6999305</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,32 +2571,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133573142</v>
+        <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>98043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>635475</v>
+        <v>635628</v>
       </c>
       <c r="R19" t="n">
-        <v>6999305</v>
+        <v>6999359</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,46 +2678,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133573133</v>
+        <v>133566413</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635907</v>
+        <v>635479</v>
       </c>
       <c r="R20" t="n">
-        <v>6999335</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2760,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2770,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,25 +2774,40 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>56539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,26 +2815,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2836,13 +2847,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R21" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2871,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2881,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,66 +2901,50 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133573147</v>
+        <v>133566401</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2959,13 +2954,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635417</v>
+        <v>635730</v>
       </c>
       <c r="R22" t="n">
-        <v>6999294</v>
+        <v>6999349</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3004,7 +2999,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3019,60 +3014,72 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133566401</v>
+        <v>133573133</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635730</v>
+        <v>635907</v>
       </c>
       <c r="R23" t="n">
-        <v>6999349</v>
+        <v>6999335</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3101,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3111,7 +3118,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3120,75 +3127,64 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573146</v>
+        <v>133573147</v>
       </c>
       <c r="B24" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635417</v>
       </c>
       <c r="R24" t="n">
-        <v>6999309</v>
+        <v>6999294</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3220,7 +3216,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,7 +3226,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,7 +3235,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3258,42 +3253,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133566414</v>
+        <v>133573146</v>
       </c>
       <c r="B25" t="n">
-        <v>56539</v>
+        <v>99178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3304,10 +3303,10 @@
         <v>635429</v>
       </c>
       <c r="R25" t="n">
-        <v>6999308</v>
+        <v>6999309</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3345,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3355,28 +3354,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566413</v>
+        <v>133573141</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635479</v>
+        <v>635507</v>
       </c>
       <c r="R26" t="n">
-        <v>6999292</v>
+        <v>6999312</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,38 +3471,38 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>93254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,45 +3510,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R27" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3594,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>93254</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,37 +3617,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R28" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,57 +3709,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>56539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R29" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3791,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,53 +3836,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566411</v>
+        <v>133566406</v>
       </c>
       <c r="B30" t="n">
-        <v>56539</v>
+        <v>91920</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635479</v>
+        <v>635550</v>
       </c>
       <c r="R30" t="n">
-        <v>6999292</v>
+        <v>6999336</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133573137</v>
+        <v>133566409</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635611</v>
+        <v>635505</v>
       </c>
       <c r="R3" t="n">
-        <v>6999361</v>
+        <v>6999294</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133566409</v>
+        <v>133573137</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635505</v>
+        <v>635611</v>
       </c>
       <c r="R4" t="n">
-        <v>6999294</v>
+        <v>6999361</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B27" t="n">
-        <v>93254</v>
+        <v>57162</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,37 +3510,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R27" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3569,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,22 +3602,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B28" t="n">
-        <v>57162</v>
+        <v>93254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,45 +3625,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R28" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,12 +3709,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133566409</v>
+        <v>133573137</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>635505</v>
+        <v>635611</v>
       </c>
       <c r="R3" t="n">
-        <v>6999294</v>
+        <v>6999361</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133573137</v>
+        <v>133566409</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>635611</v>
+        <v>635505</v>
       </c>
       <c r="R4" t="n">
-        <v>6999361</v>
+        <v>6999294</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,12 +984,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R14" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R15" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566413</v>
+        <v>133566414</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>56539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,26 +2689,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2716,10 +2721,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635479</v>
+        <v>635429</v>
       </c>
       <c r="R20" t="n">
-        <v>6999292</v>
+        <v>6999308</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2751,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2761,7 +2766,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2770,24 +2775,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2804,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133566414</v>
+        <v>133566401</v>
       </c>
       <c r="B21" t="n">
-        <v>56539</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,42 +2804,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635429</v>
+        <v>635730</v>
       </c>
       <c r="R21" t="n">
-        <v>6999308</v>
+        <v>6999349</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2882,7 +2863,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2873,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,48 +2900,60 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133566401</v>
+        <v>133573133</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635730</v>
+        <v>635907</v>
       </c>
       <c r="R22" t="n">
-        <v>6999349</v>
+        <v>6999335</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2989,7 +2982,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2999,7 +2992,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,78 +3001,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133573133</v>
+        <v>133573147</v>
       </c>
       <c r="B23" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>635907</v>
+        <v>635417</v>
       </c>
       <c r="R23" t="n">
-        <v>6999335</v>
+        <v>6999294</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3108,7 +3090,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,7 +3100,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,7 +3109,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3146,45 +3127,57 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573147</v>
+        <v>133573146</v>
       </c>
       <c r="B24" t="n">
-        <v>91920</v>
+        <v>99178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635417</v>
+        <v>635429</v>
       </c>
       <c r="R24" t="n">
-        <v>6999294</v>
+        <v>6999309</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3216,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3226,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,6 +3228,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3253,46 +3247,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573146</v>
+        <v>133573141</v>
       </c>
       <c r="B25" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3300,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R25" t="n">
-        <v>6999309</v>
+        <v>6999312</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3335,7 +3320,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3330,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,6 +3342,21 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133573141</v>
+        <v>133566413</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,21 +3384,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635507</v>
+        <v>635479</v>
       </c>
       <c r="R26" t="n">
-        <v>6999312</v>
+        <v>6999292</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,28 +3471,28 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 37126-2025 artfynd.xlsx
+++ b/artfynd/A 37126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133573144</v>
       </c>
       <c r="B2" t="n">
-        <v>80477</v>
+        <v>80478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133573137</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>133566409</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133566404</v>
       </c>
       <c r="B5" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>133573143</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>133573136</v>
       </c>
       <c r="B7" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1456,45 +1456,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133566419</v>
+        <v>133566392</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>635425</v>
+        <v>635950</v>
       </c>
       <c r="R9" t="n">
-        <v>6999291</v>
+        <v>6999346</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133566392</v>
+        <v>133566416</v>
       </c>
       <c r="B10" t="n">
         <v>57162</v>
@@ -1596,7 +1604,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>635950</v>
+        <v>635420</v>
       </c>
       <c r="R10" t="n">
-        <v>6999346</v>
+        <v>6999295</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,53 +1686,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133566416</v>
+        <v>133566419</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>91959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>635420</v>
+        <v>635425</v>
       </c>
       <c r="R11" t="n">
-        <v>6999295</v>
+        <v>6999291</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,7 +1911,7 @@
         <v>133573139</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133566407</v>
+        <v>133573134</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>635554</v>
+        <v>635894</v>
       </c>
       <c r="R14" t="n">
-        <v>6999318</v>
+        <v>6999387</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,22 +2123,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133573134</v>
+        <v>133566407</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>635894</v>
+        <v>635554</v>
       </c>
       <c r="R15" t="n">
-        <v>6999387</v>
+        <v>6999318</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,12 +2230,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
         <v>133573132</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>133573142</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>133573138</v>
       </c>
       <c r="B19" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133566414</v>
+        <v>133566413</v>
       </c>
       <c r="B20" t="n">
-        <v>56539</v>
+        <v>91959</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,31 +2689,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2721,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>635429</v>
+        <v>635479</v>
       </c>
       <c r="R20" t="n">
-        <v>6999308</v>
+        <v>6999292</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2756,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2775,8 +2770,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2793,48 +2804,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133566401</v>
+        <v>133573133</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>99180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>635730</v>
+        <v>635907</v>
       </c>
       <c r="R21" t="n">
-        <v>6999349</v>
+        <v>6999335</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2863,7 +2886,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,7 +2896,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,28 +2905,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133573133</v>
+        <v>133573146</v>
       </c>
       <c r="B22" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2954,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2947,13 +2971,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>635907</v>
+        <v>635429</v>
       </c>
       <c r="R22" t="n">
-        <v>6999335</v>
+        <v>6999309</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2982,7 +3006,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2992,7 +3016,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3023,7 +3047,7 @@
         <v>133573147</v>
       </c>
       <c r="B23" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,46 +3151,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133573146</v>
+        <v>133573141</v>
       </c>
       <c r="B24" t="n">
-        <v>99178</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3174,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>635429</v>
+        <v>635507</v>
       </c>
       <c r="R24" t="n">
-        <v>6999309</v>
+        <v>6999312</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3209,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,6 +3246,21 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3247,10 +3277,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133573141</v>
+        <v>133566414</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>56539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3258,26 +3288,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3285,13 +3320,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>635507</v>
+        <v>635429</v>
       </c>
       <c r="R25" t="n">
-        <v>6999312</v>
+        <v>6999308</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3320,7 +3355,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3330,7 +3365,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,44 +3374,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133566413</v>
+        <v>133566401</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,37 +3403,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>635479</v>
+        <v>635730</v>
       </c>
       <c r="R26" t="n">
-        <v>6999292</v>
+        <v>6999349</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3446,7 +3462,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3456,7 +3472,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,24 +3481,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3499,10 +3499,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133566402</v>
+        <v>133573150</v>
       </c>
       <c r="B27" t="n">
-        <v>57162</v>
+        <v>93256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,45 +3510,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>635721</v>
+        <v>635339</v>
       </c>
       <c r="R27" t="n">
-        <v>6999345</v>
+        <v>6999315</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3577,7 +3569,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,7 +3579,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,22 +3594,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133573150</v>
+        <v>133566402</v>
       </c>
       <c r="B28" t="n">
-        <v>93254</v>
+        <v>57162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3625,37 +3617,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>635339</v>
+        <v>635721</v>
       </c>
       <c r="R28" t="n">
-        <v>6999315</v>
+        <v>6999345</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,22 +3709,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133566411</v>
+        <v>133573145</v>
       </c>
       <c r="B29" t="n">
-        <v>56539</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3732,31 +3732,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3764,13 +3759,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>635479</v>
+        <v>635465</v>
       </c>
       <c r="R29" t="n">
-        <v>6999292</v>
+        <v>6999358</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3799,7 +3794,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3804,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,63 +3813,87 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133566406</v>
+        <v>133566411</v>
       </c>
       <c r="B30" t="n">
-        <v>91920</v>
+        <v>56539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>206004</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>635550</v>
+        <v>635479</v>
       </c>
       <c r="R30" t="n">
-        <v>6999336</v>
+        <v>6999292</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3916,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3943,51 +3962,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133573145</v>
+        <v>133566406</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>91922</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjuvtoberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>635465</v>
+        <v>635550</v>
       </c>
       <c r="R31" t="n">
-        <v>6999358</v>
+        <v>6999336</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4016,7 +4032,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4042,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,34 +4051,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
         <v>133573140</v>
       </c>
       <c r="B32" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
